--- a/InputData/elec/BBPPRTY/BAU Ban Power Plant Retrofits This Year.xlsx
+++ b/InputData/elec/BBPPRTY/BAU Ban Power Plant Retrofits This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\BBPPRTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\elec\BBPPRTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044A0703-5029-44F0-AB81-97DA410ABD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEE8D36-A5B6-4C7C-951F-73A5CD877B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12345" yWindow="1170" windowWidth="27360" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27285" yWindow="1515" windowWidth="22290" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2356,14 +2356,14 @@
       <c r="H19">
         <v>1</v>
       </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0</v>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
       </c>
       <c r="L19" s="5">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>1</v>
       </c>
       <c r="I20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="5">
         <v>0</v>
@@ -2547,13 +2547,13 @@
         <v>1</v>
       </c>
       <c r="I21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>1</v>
       </c>
       <c r="I22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="5">
         <v>0</v>
